--- a/game/design/characters/students.xlsx
+++ b/game/design/characters/students.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -484,18 +484,14 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -541,45 +537,25 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Что делает после универа</t>
+          <t>Характер</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>С кем дружит</t>
+          <t>Любимая фраза</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Характер</t>
+          <t>Внешность (пришлю фото)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Любимая фраза</t>
+          <t>Сдаст курс?</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Внешность</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Чем поможет герою</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Сдаст курс?</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Своя история в игре</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Заметки</t>
         </is>
@@ -607,32 +583,44 @@
           <t>редко</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>в столовке в курилке в общаге на парах</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>добрая, взрослая</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>ТУпить</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>добрая, взрослая</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="n"/>
+          <t>невысокая, ~150 см. Бледная Очки и брюнетка</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>точно сдаст</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>невысокая, ~150 см</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>точно сдаст</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>старше всех, уже училась на мехмате; преподы не любят за пропуски</t>
+          <t>старше всех, уже училась на мехмате; преподы не любят за пропуски; Чем интересен: Может дать сигарету, Помочь если сидишь сзади, РАссказать легенду или Шутку пошутить Рассказать о других; Своя история: полная</t>
         </is>
       </c>
     </row>
@@ -653,27 +641,51 @@
       <c r="D3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>часто</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>обычная, иногда поможет</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Даша (со временем)</t>
+          <t>Хз</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>обычная, иногда поможет</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
+          <t>Очки Метр 165 Брюнетка свободный стиль</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>скорее вылетит</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Чем интересен: Ничем поможет только списать мейби можно поговорить; Дружит: Даша (со временем)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -694,35 +706,47 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>иногда</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+          <t>редко</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>В столовые в курилке в общаге на парах</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>харизматичный, умный, всегда есть что сказать</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Справедливости ради</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>харизматичный, умный, всегда есть что сказать</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="n"/>
+          <t>высокий, чуть полноват. 185 см рост брюнет</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>точно сдаст</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>высокий, чуть полноват</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>точно сдаст</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>ровесник Адины</t>
+          <t>ровесник Адины; Чем интересен: Истории интересные, английский понатаскать. Тоде сигарету. Рассказать о других</t>
         </is>
       </c>
     </row>
@@ -748,26 +772,46 @@
           <t>часто</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>сдержанный, учёба не нравится</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Не знаю (короткое)</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>сдержанный, учёба не нравится</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n"/>
+          <t>высокий Блондин</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>высокий блондин</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
+          <t>Чем интересен: О увлечениях что строит саморучно машину. Приколы</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -791,24 +835,40 @@
           <t>часто</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>творческий, скромный добряк</t>
         </is>
       </c>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>играет на инструментах</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Бро</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>скорее вылетит</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>играет на инструментах; Чем интересен: ИГрает на интсурметах что по этому поводу и если что помочь списать</t>
         </is>
       </c>
     </row>
@@ -834,28 +894,40 @@
           <t>всегда</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>скучный, почти не смеётся</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>нет (фон)</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>только универ и дом; разговор не поддержит</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>(Заикается)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>точно вылетит</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>только универ и дом; разговор не поддержит; Чем интересен: Ничего; Своя история: нет (фон)</t>
         </is>
       </c>
     </row>
@@ -881,24 +953,40 @@
           <t>редко</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>милая, но ругается жёстко</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>чёрный юмор про смерть — просто манера шутить</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>милая, но ругается матом. Любит няшные вещи</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>(Любой мат)</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>чёрный юмор про смерть — просто манера шутить; Чем интересен: Игры милые. МУзыка и тоже историии приколы</t>
         </is>
       </c>
     </row>
@@ -924,26 +1012,42 @@
           <t>волнами</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>сдержанный, любит дискуссии. Поиграть в комп</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Серьезно?</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>сдержанный, любит дискуссии</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n"/>
+          <t>высокий, кудрявый, в очках</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>скорее сдаст</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>высокий, кудрявый, в очках</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>гум. школа, на год старше, играет в комп</t>
         </is>
@@ -971,22 +1075,38 @@
           <t>иногда</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>зоркая, делится, поддержит разговор</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Бро</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1010,22 +1130,34 @@
           <t>часто</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в курилке и в общаге</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>хорошая, добрая. Поможет подскажет. Смешная иногда</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="n"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>хорошая, добрая</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1049,22 +1181,34 @@
           <t>часто</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>умная, немного странная. Добрая  сдержанная</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="n"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>умная, немного странная</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>скорее сдаст</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>«всё может сдать»</t>
         </is>
@@ -1092,22 +1236,38 @@
           <t>часто</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>скромный, сдержанный</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в курилке</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>скромный, сдержанный. Любит музыку. Нетактичный и нетактильный. Но может поддержать разговор</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>НУуууу</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>скорее сдаст</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>редко с кем общается</t>
         </is>
@@ -1130,23 +1290,43 @@
       <c r="D14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>добрая, чуть-чуть «на себе»</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>редко</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>добрая, хорошая Тактильная (с девушками)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Хз</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1170,22 +1350,34 @@
           <t>часто</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>добрая, хорошая. Умеет поддержать разговор.</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="n"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>добрая, хорошая</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>скорее вылетит</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>в школе была отличницей, здесь тяжело</t>
         </is>
@@ -1208,29 +1400,45 @@
       <c r="D16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>всегда</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>На парах иногда в курилке</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>«крутая». Нетерпеливая. А так добрая если что поделится поможет</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Сайгуль (со временем)</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>«крутая»</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>за ней ходят мальчики</t>
+          <t>(Любые маты)</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>за ней ходят мальчики; Дружит: Сайгуль (со временем)</t>
         </is>
       </c>
     </row>
@@ -1256,30 +1464,46 @@
           <t>иногда</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>На парах в курилке</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>душа компании, громко смеётся и шутит.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>(Крутой момент сказать) Моя, Моя родная и тд</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>душа компании, громко смеётся</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="n"/>
+          <t>короткая стрижка</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>короткая стрижка</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>только дружба</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+          <t>Своя история: только дружба</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1298,27 +1522,43 @@
       <c r="D18" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>взрослый, думает медленно, но умный</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в общаге</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>взрослый, думает медленно, но умный. Шарит за многое</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Что?</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>«Сказать что? Сказать что?»</t>
+          <t>точно сдаст</t>
         </is>
       </c>
       <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1334,32 +1574,46 @@
           <t>м</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>почти никогда</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>бэд-бой, ему не надо</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в курилке</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Не посещает ничего не делает и с ничем не справляется</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Похуй</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>точно вылетит</t>
+        </is>
+      </c>
       <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>точно вылетит</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1378,23 +1632,39 @@
       <c r="D20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>всегда</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в общаге</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>скромный, необщительный, добрый. Всегда можно обратиться за помощью но ему может и надоесть.</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="n"/>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>скромный, необщительный, добрый</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>точно сдаст</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>физмат-школа</t>
         </is>
@@ -1417,23 +1687,39 @@
       <c r="D21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>всегда</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>смешная, любит внимание, но воспитанная.</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="n"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>смешная, любит внимание, но воспитанная</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>скорее сдаст</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1449,32 +1735,46 @@
           <t>ж</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>умная, ухоженная</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>почти всегда</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Ухоженная. Чем то постоянно занята.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Ент репетиторство куратор</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>точно вылетит</t>
         </is>
       </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>работает репетитором</t>
         </is>
@@ -1497,23 +1797,43 @@
       <c r="D23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>неразговорчивый, чуть «на себе»</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>редко</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>неразговорчивый, чуть «на себе». Готовится поступить в тайвань</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Тайвань</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>собирается в Тайвань</t>
         </is>
@@ -1536,23 +1856,43 @@
       <c r="D24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в курилке и в общаге</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>умная, темперамент «торнадо»</t>
         </is>
       </c>
-      <c r="L24" s="3" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>(Все маты)</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>скорее сдаст</t>
+        </is>
+      </c>
       <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1571,23 +1911,43 @@
       <c r="D25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>душа компании, шутит</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>всегда</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>На парах в курилке</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>душа компании, шутит. Не со всеми ладит</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Всякое что то с Германий</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>скорее вылетит</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>гум. школа, учёбу не потянет</t>
         </is>
@@ -1610,23 +1970,39 @@
       <c r="D26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>часто</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>На парах и в общаге</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>хорошая, добрая</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="n"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>хорошая, добрая</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>зависит от героя</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>всё списывает</t>
         </is>
@@ -1654,29 +2030,45 @@
           <t>всегда</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>очень старательная</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>никогда</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>На парах только</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>очень старательная. Добрая</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Вы же должны были</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>скорее сдаст</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>общается с преподами</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation sqref="E2:E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"всегда,часто,иногда,редко,почти никогда,волнами"</formula1>
     </dataValidation>
@@ -1686,11 +2078,8 @@
     <dataValidation sqref="G2:G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,нет,иногда"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"точно сдаст,скорее сдаст,зависит от героя,скорее вылетит,точно вылетит"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P2:P27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"полная,короткая,только дружба,нет (фон)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1703,10 +2092,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1726,91 +2115,55 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>пустые — их и надо дописать. Можно писать своими словами.</t>
+          <t>пустые — можно дописать своими словами.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Колонки с выпадающим списком</t>
+          <t>Выпадающие списки</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>«Как часто на парах», «Опаздывает?», «Курит?», «Сдаст курс?», «Своя история» — можно выбрать из списка или написать своё.</t>
+          <t>«Как часто на парах», «Опаздывает?», «Курит?», «Сдаст курс?» — можно выбрать из списка или написать своё.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Где его обычно увидишь</t>
+          <t>Где увидишь</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>например: курилка, столовая, библиотека, подоконник у аудитории, почти не бывает</t>
+          <t>встретить можно где угодно, если человеку туда надо; тут — где он бывает чаще всего</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Что делает после универа</t>
+          <t>После пар</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>например: работа, спорт, домой спать, гуляет с друзьями, репетиторство</t>
+          <t>общее правило: все идут в общагу или домой</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Чем поможет герою</t>
+          <t>Сдаст курс?</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>например: даст списать, расскажет слухи, позовёт на гулянку, объяснит задачу</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Сдаст курс?</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>итог должен быть такой: после 1 семестра остаются 18 человек, после 2-го — 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Своя история в игре</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>полная — длинная история с концовкой (на всю игру 5–7 человек); короткая — 2–3 сцены</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Пример заполненной строки</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>ходит: иногда · опаздывает: почти всегда · курит: нет · где увидишь: столовая · после универа: гуляет · дружит с: Адина · поможет: позовёт на гулянку</t>
+          <t>после 1 семестра остаются 18 человек, после 2-го — 16 (вылетают 10)</t>
         </is>
       </c>
     </row>

--- a/game/design/characters/students.xlsx
+++ b/game/design/characters/students.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Одногруппники" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Как заполнять" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Вопросы" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47,7 +48,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="003B4252"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D5B"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,9 +97,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,6 +118,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -491,10 +503,15 @@
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
@@ -555,1520 +572,1679 @@
           <t>Сдаст курс?</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Харизма (0–10)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>О чём с ним интересно говорить</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>О чём лучше не говорить / что бесит</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Может быть любовь с героем?</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Реальный случай с ним (для ивента)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Заметки</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Адина</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>в столовке в курилке в общаге на парах</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>добрая, взрослая</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>ТУпить</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>невысокая, ~150 см. Бледная Очки и брюнетка</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>точно сдаст</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>старше всех, уже училась на мехмате; преподы не любят за пропуски; Чем интересен: Может дать сигарету, Помочь если сидишь сзади, РАссказать легенду или Шутку пошутить Рассказать о других; Своя история: полная</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Сайгуль</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>обычная, иногда поможет</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Хз</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Очки Метр 165 Брюнетка свободный стиль</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>скорее вылетит</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Чем интересен: Ничем поможет только списать мейби можно поговорить; Дружит: Даша (со временем)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Ноидор</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>В столовые в курилке в общаге на парах</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>харизматичный, умный, всегда есть что сказать</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Справедливости ради</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>высокий, чуть полноват. 185 см рост брюнет</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>точно сдаст</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>ровесник Адины; Чем интересен: Истории интересные, английский понатаскать. Тоде сигарету. Рассказать о других</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Кирлан</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>сдержанный, учёба не нравится</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Не знаю (короткое)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>высокий Блондин</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Чем интересен: О увлечениях что строит саморучно машину. Приколы</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Бауржан</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>творческий, скромный добряк</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Бро</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>скорее вылетит</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>играет на инструментах; Чем интересен: ИГрает на интсурметах что по этому поводу и если что помочь списать</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Руслан</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>всегда</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>скучный, почти не смеётся</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>(Заикается)</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>точно вылетит</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>только универ и дом; разговор не поддержит; Чем интересен: Ничего; Своя история: нет (фон)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Мирис</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>милая, но ругается матом. Любит няшные вещи</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>(Любой мат)</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>чёрный юмор про смерть — просто манера шутить; Чем интересен: Игры милые. МУзыка и тоже историии приколы</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Аланас</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>волнами</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>сдержанный, любит дискуссии. Поиграть в комп</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Серьезно?</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>высокий, кудрявый, в очках</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>скорее сдаст</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>гум. школа, на год старше, играет в комп</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Азиза</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>зоркая, делится, поддержит разговор</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Бро</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M10" s="3" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Аделия</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>На парах и в курилке и в общаге</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>хорошая, добрая. Поможет подскажет. Смешная иногда</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M11" s="3" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Света</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>умная, немного странная. Добрая  сдержанная</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>скорее сдаст</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>«всё может сдать»</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Исан</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>На парах и в курилке</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>скромный, сдержанный. Любит музыку. Нетактичный и нетактильный. Но может поддержать разговор</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>НУуууу</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>скорее сдаст</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>редко с кем общается</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Катарина</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>добрая, хорошая Тактильная (с девушками)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Хз</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M14" s="3" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Гаухар</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>добрая, хорошая. Умеет поддержать разговор.</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>скорее вылетит</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>в школе была отличницей, здесь тяжело</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Даша</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>всегда</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>На парах иногда в курилке</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>«крутая». Нетерпеливая. А так добрая если что поделится поможет</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>(Любые маты)</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>за ней ходят мальчики; Дружит: Сайгуль (со временем)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Адалина</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>На парах в курилке</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>душа компании, громко смеётся и шутит.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>(Крутой момент сказать) Моя, Моя родная и тд</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>короткая стрижка</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>Своя история: только дружба</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Сендир</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>На парах и в общаге</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>взрослый, думает медленно, но умный. Шарит за многое</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Что?</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>точно сдаст</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Алнар</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>почти никогда</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>На парах и в курилке</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Не посещает ничего не делает и с ничем не справляется</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Похуй</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>точно вылетит</t>
         </is>
       </c>
-      <c r="M19" s="3" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Саид</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>всегда</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>На парах и в общаге</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>скромный, необщительный, добрый. Всегда можно обратиться за помощью но ему может и надоесть.</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>точно сдаст</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>физмат-школа</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Назель</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>всегда</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>смешная, любит внимание, но воспитанная.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>скорее сдаст</t>
         </is>
       </c>
-      <c r="M21" s="3" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Мадина</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>почти всегда</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Ухоженная. Чем то постоянно занята.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Ент репетиторство куратор</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>точно вылетит</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>работает репетитором</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Амир</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>редко</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>неразговорчивый, чуть «на себе». Готовится поступить в тайвань</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Тайвань</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>собирается в Тайвань</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Вика</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>На парах и в курилке и в общаге</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>умная, темперамент «торнадо»</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>(Все маты)</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>скорее сдаст</t>
         </is>
       </c>
-      <c r="M24" s="3" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Даниил</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>всегда</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>На парах в курилке</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>душа компании, шутит. Не со всеми ладит</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Всякое что то с Германий</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>скорее вылетит</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>гум. школа, учёбу не потянет</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Талвина</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>часто</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>На парах и в общаге</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>хорошая, добрая</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>зависит от героя</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>всё списывает</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Карина</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>ж</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>всегда</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>никогда</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>На парах только</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>очень старательная. Добрая</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Вы же должны были</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>скорее сдаст</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>общается с преподами</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="E2:E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"всегда,часто,иногда,редко,почти никогда,волнами"</formula1>
     </dataValidation>
@@ -2081,6 +2257,9 @@
     <dataValidation sqref="L2:L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"точно сдаст,скорее сдаст,зависит от героя,скорее вылетит,точно вылетит"</formula1>
     </dataValidation>
+    <dataValidation sqref="P2:P27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"да,нет,только дружба"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2092,80 +2271,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Как заполнять</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr"/>
+      <c r="B1" s="6" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Жёлтые клетки</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>пустые — можно дописать своими словами.</t>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>пустые — дописать своими словами.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Выпадающие списки</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>«Как часто на парах», «Опаздывает?», «Курит?», «Сдаст курс?» — можно выбрать из списка или написать своё.</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Зелёные заголовки</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>новые столбцы — их ещё никто не заполнял.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Где увидишь</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>встретить можно где угодно, если человеку туда надо; тут — где он бывает чаще всего</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Харизма</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>0–10: насколько легко с ним говорить, зовут ли его на гулянки. Например, у Ноидора высокая — 8.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>После пар</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>общее правило: все идут в общагу или домой</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>О чём интересно говорить</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>темы для разговоров на перерыве: машины, музыка, игры, сплетни, учёба. Верная тема — разговор удался.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Сдаст курс?</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>после 1 семестра остаются 18 человек, после 2-го — 16 (вылетают 10)</t>
-        </is>
-      </c>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>О чём лучше не говорить</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>что его бесит или ставит в неловкость. Такая тема — разговор провален.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Может быть любовь?</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>любовь в игре — только с противоположным полом. «только дружба» — любовной линии нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Реальный случай</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>что было на самом деле и что можно превратить в ивент. Можно коротко: «принесла торт на пару».</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Лист «Вопросы»</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>общие вопросы — ответь одной строкой.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Твой ответ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Мат: у Мирис, Даши, Вики, Алнара фраза — мат. Писать как есть, смягчать («блин») или запикивать (***)?</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Даниил: шутки про Германию намекают на настоящее имя. Оставить или другая фишка?</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Руслан заикается: показываем бережно, не как повод для шуток — ок?</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Полные линии: у кого ещё, кроме Адины? Всего 5–7 человек.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Кто в какой компании стоит на перерыве? (можно списком: «Адина, Ноидор, Вика — курилка»)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Фото для внешности — пришлёшь?</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
